--- a/astro-site/public/dl/kit-tareas-pasteleria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/01-apertura-cierre.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Apertura Obrador" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Cierre Obrador" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Apertura Obrador" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cierre Obrador" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Apertura Obrador'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Cierre Obrador'!$4:$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -91,6 +94,12 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="00333333"/>
+      <sz val="11"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -130,7 +139,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -152,59 +161,109 @@
         <color rgb="00E0E0E0"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E0E0E0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E0E0E0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E0E0E0"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="29">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="3" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="3" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="5" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="1" fillId="6" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -566,13 +625,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B12"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -580,6 +640,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -608,9 +669,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -639,8 +698,24 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
 </file>
 
@@ -649,18 +724,18 @@
   <sheetPr>
     <tabColor rgb="00FF8C00"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -677,10 +752,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -720,18 +796,16 @@
           <t xml:space="preserve">  Encendido de Equipos</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -757,10 +831,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="28" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -786,10 +858,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -815,10 +885,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="28" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -844,10 +912,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -873,10 +939,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="28" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -902,10 +966,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="28" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -930,24 +992,23 @@
       <c r="F12" s="14" t="n"/>
       <c r="G12" s="15" t="n"/>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="7" t="inlineStr">
         <is>
           <t xml:space="preserve">  Preparación del Obrador</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="8" t="n"/>
-      <c r="D14" s="8" t="n"/>
-      <c r="E14" s="8" t="n"/>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
+      <c r="F14" s="26" t="n"/>
+      <c r="G14" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A15" s="28" t="n">
+        <v>8</v>
       </c>
       <c r="B15" s="10" t="inlineStr">
         <is>
@@ -973,10 +1034,8 @@
       <c r="G15" s="15" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A16" s="28" t="n">
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="inlineStr">
         <is>
@@ -1002,10 +1061,8 @@
       <c r="G16" s="15" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="28" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1031,10 +1088,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="28" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1060,10 +1115,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="28" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1089,10 +1142,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="28" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1118,10 +1169,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="28" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1147,10 +1196,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="28" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1175,24 +1222,23 @@
       <c r="F22" s="14" t="n"/>
       <c r="G22" s="15" t="n"/>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Apertura Vitrina / Despacho</t>
         </is>
       </c>
-      <c r="B24" s="17" t="n"/>
-      <c r="C24" s="17" t="n"/>
-      <c r="D24" s="17" t="n"/>
-      <c r="E24" s="17" t="n"/>
-      <c r="F24" s="17" t="n"/>
-      <c r="G24" s="17" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="27" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A25" s="28" t="n">
+        <v>16</v>
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
@@ -1218,10 +1264,8 @@
       <c r="G25" s="15" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="28" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -1247,10 +1291,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="28" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -1276,10 +1318,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="28" t="n">
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -1305,10 +1345,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="28" t="n">
+        <v>20</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -1334,10 +1372,8 @@
       <c r="G29" s="15" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A30" s="28" t="n">
+        <v>21</v>
       </c>
       <c r="B30" s="10" t="inlineStr">
         <is>
@@ -1363,10 +1399,8 @@
       <c r="G30" s="15" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A31" s="28" t="n">
+        <v>22</v>
       </c>
       <c r="B31" s="10" t="inlineStr">
         <is>
@@ -1391,6 +1425,8 @@
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="15" t="n"/>
     </row>
+    <row r="32"/>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -1399,7 +1435,7 @@
       </c>
       <c r="D34" s="19">
         <f>COUNTIF(F5:F32,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E34" s="20" t="inlineStr">
         <is>
@@ -1410,6 +1446,7 @@
         <v>22</v>
       </c>
     </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="19" t="inlineStr">
         <is>
@@ -1417,13 +1454,17 @@
         </is>
       </c>
       <c r="B36" s="15" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="27" t="n"/>
       <c r="E36" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F36" s="15" t="n"/>
-    </row>
+      <c r="G36" s="27" t="n"/>
+    </row>
+    <row r="37"/>
     <row r="38">
       <c r="A38" s="21" t="inlineStr">
         <is>
@@ -1443,11 +1484,20 @@
     <mergeCell ref="B36:D36"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F21 F22 F25 F26 F27 F28 F29 F30 F31" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F21 F22 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1456,18 +1506,18 @@
   <sheetPr>
     <tabColor rgb="008B4513"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="12"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1484,10 +1534,11 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>☐</t>
+          <t>Nº</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
@@ -1527,18 +1578,16 @@
           <t xml:space="preserve">  Cierre de Producción</t>
         </is>
       </c>
-      <c r="B5" s="8" t="n"/>
-      <c r="C5" s="8" t="n"/>
-      <c r="D5" s="8" t="n"/>
-      <c r="E5" s="8" t="n"/>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
+      <c r="B5" s="26" t="n"/>
+      <c r="C5" s="26" t="n"/>
+      <c r="D5" s="26" t="n"/>
+      <c r="E5" s="26" t="n"/>
+      <c r="F5" s="26" t="n"/>
+      <c r="G5" s="27" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A6" s="28" t="n">
+        <v>1</v>
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
@@ -1564,10 +1613,8 @@
       <c r="G6" s="15" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A7" s="28" t="n">
+        <v>2</v>
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
@@ -1593,10 +1640,8 @@
       <c r="G7" s="15" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A8" s="28" t="n">
+        <v>3</v>
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
@@ -1622,10 +1667,8 @@
       <c r="G8" s="15" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A9" s="28" t="n">
+        <v>4</v>
       </c>
       <c r="B9" s="10" t="inlineStr">
         <is>
@@ -1651,10 +1694,8 @@
       <c r="G9" s="15" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A10" s="28" t="n">
+        <v>5</v>
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
@@ -1680,10 +1721,8 @@
       <c r="G10" s="15" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A11" s="28" t="n">
+        <v>6</v>
       </c>
       <c r="B11" s="10" t="inlineStr">
         <is>
@@ -1709,10 +1748,8 @@
       <c r="G11" s="15" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A12" s="28" t="n">
+        <v>7</v>
       </c>
       <c r="B12" s="10" t="inlineStr">
         <is>
@@ -1738,10 +1775,8 @@
       <c r="G12" s="15" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A13" s="28" t="n">
+        <v>8</v>
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
@@ -1767,10 +1802,8 @@
       <c r="G13" s="15" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A14" s="28" t="n">
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="inlineStr">
         <is>
@@ -1795,24 +1828,23 @@
       <c r="F14" s="14" t="n"/>
       <c r="G14" s="15" t="n"/>
     </row>
+    <row r="15"/>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre Vitrina / Despacho</t>
         </is>
       </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="17" t="n"/>
-      <c r="D16" s="17" t="n"/>
-      <c r="E16" s="17" t="n"/>
-      <c r="F16" s="17" t="n"/>
-      <c r="G16" s="17" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="27" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A17" s="28" t="n">
+        <v>10</v>
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
@@ -1838,10 +1870,8 @@
       <c r="G17" s="15" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A18" s="28" t="n">
+        <v>11</v>
       </c>
       <c r="B18" s="10" t="inlineStr">
         <is>
@@ -1867,10 +1897,8 @@
       <c r="G18" s="15" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A19" s="28" t="n">
+        <v>12</v>
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
@@ -1896,10 +1924,8 @@
       <c r="G19" s="15" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A20" s="28" t="n">
+        <v>13</v>
       </c>
       <c r="B20" s="10" t="inlineStr">
         <is>
@@ -1925,10 +1951,8 @@
       <c r="G20" s="15" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A21" s="28" t="n">
+        <v>14</v>
       </c>
       <c r="B21" s="10" t="inlineStr">
         <is>
@@ -1954,10 +1978,8 @@
       <c r="G21" s="15" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A22" s="28" t="n">
+        <v>15</v>
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
@@ -1983,10 +2005,8 @@
       <c r="G22" s="15" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A23" s="28" t="n">
+        <v>16</v>
       </c>
       <c r="B23" s="10" t="inlineStr">
         <is>
@@ -2011,24 +2031,23 @@
       <c r="F23" s="14" t="n"/>
       <c r="G23" s="15" t="n"/>
     </row>
+    <row r="24"/>
     <row r="25">
       <c r="A25" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">  Cierre General</t>
         </is>
       </c>
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="23" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
-      <c r="F25" s="23" t="n"/>
-      <c r="G25" s="23" t="n"/>
+      <c r="B25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="26" t="n"/>
+      <c r="E25" s="26" t="n"/>
+      <c r="F25" s="26" t="n"/>
+      <c r="G25" s="27" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A26" s="28" t="n">
+        <v>17</v>
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
@@ -2054,10 +2073,8 @@
       <c r="G26" s="15" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A27" s="28" t="n">
+        <v>18</v>
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
@@ -2083,10 +2100,8 @@
       <c r="G27" s="15" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A28" s="28" t="n">
+        <v>19</v>
       </c>
       <c r="B28" s="10" t="inlineStr">
         <is>
@@ -2112,10 +2127,8 @@
       <c r="G28" s="15" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>☐</t>
-        </is>
+      <c r="A29" s="28" t="n">
+        <v>20</v>
       </c>
       <c r="B29" s="10" t="inlineStr">
         <is>
@@ -2140,6 +2153,8 @@
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="15" t="n"/>
     </row>
+    <row r="30"/>
+    <row r="31"/>
     <row r="32">
       <c r="A32" s="19" t="inlineStr">
         <is>
@@ -2148,7 +2163,7 @@
       </c>
       <c r="D32" s="19">
         <f>COUNTIF(F5:F30,"✓")</f>
-        <v/>
+        <v>0.0</v>
       </c>
       <c r="E32" s="20" t="inlineStr">
         <is>
@@ -2159,6 +2174,7 @@
         <v>20</v>
       </c>
     </row>
+    <row r="33"/>
     <row r="34">
       <c r="A34" s="19" t="inlineStr">
         <is>
@@ -2166,13 +2182,17 @@
         </is>
       </c>
       <c r="B34" s="15" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="27" t="n"/>
       <c r="E34" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F34" s="15" t="n"/>
-    </row>
+      <c r="G34" s="27" t="n"/>
+    </row>
+    <row r="35"/>
     <row r="36">
       <c r="A36" s="21" t="inlineStr">
         <is>
@@ -2192,10 +2212,19 @@
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F22 F23 F26 F27 F28 F29" type="list">
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F22 F23 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"✓,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-pasteleria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/01-apertura-cierre.xlsx
@@ -263,6 +263,16 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -702,14 +712,15 @@
     <row r="14">
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>Marca con ✓ en la columna «Hecha» (desplegable): es la que cuenta el total de tareas completadas.</t>
-        </is>
-      </c>
-    </row>
+          <t>Marca con ✓ en la columna «✓ Completada» (desplegable): es la que cuenta el total de tareas completadas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
     <row r="16">
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -726,7 +737,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G38"/>
+  <dimension ref="A1:G41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -781,7 +792,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -917,7 +928,7 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>Verificar temperatura de cámaras frigoríficas (registrar)</t>
+          <t>Verificar temperatura de cámaras frigoríficas (registrar) → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1242,7 +1253,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Encender iluminación y climatización de vitrinas</t>
+          <t>Encender las vitrinas refrigeradas y comprobar que están a 2-6 °C antes de montar → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
@@ -1257,7 +1268,7 @@
       </c>
       <c r="E25" s="13" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="F25" s="14" t="n"/>
@@ -1269,7 +1280,7 @@
       </c>
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Colocar productos del día anterior (verificar caducidad)</t>
+          <t>Colocar la producción del día; el producto del día anterior solo en la zona de promoción señalizada o a merma → 10 Plan de Producción Semanal · hoja Producido vs Vendido · 13 Registro de Temperaturas · Vidas Útiles</t>
         </is>
       </c>
       <c r="C26" s="18" t="inlineStr">
@@ -1284,7 +1295,7 @@
       </c>
       <c r="E26" s="13" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:45</t>
         </is>
       </c>
       <c r="F26" s="14" t="n"/>
@@ -1296,7 +1307,7 @@
       </c>
       <c r="B27" s="10" t="inlineStr">
         <is>
-          <t>Preparar etiquetas de precio y alérgenos</t>
+          <t>Preparar etiquetas de precio y alérgenos → 12 Control de Alérgenos de Vitrina</t>
         </is>
       </c>
       <c r="C27" s="18" t="inlineStr">
@@ -1425,48 +1436,84 @@
       <c r="F31" s="14" t="n"/>
       <c r="G31" s="15" t="n"/>
     </row>
-    <row r="32"/>
-    <row r="33"/>
+    <row r="32">
+      <c r="A32" s="28" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
     <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="10" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="12" t="n"/>
+      <c r="E34" s="13" t="n"/>
+      <c r="F34" s="14" t="n"/>
+      <c r="G34" s="15" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="28" t="n"/>
+      <c r="B35" s="10" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="12" t="n"/>
+      <c r="E35" s="13" t="n"/>
+      <c r="F35" s="14" t="n"/>
+      <c r="G35" s="15" t="n"/>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D34" s="19">
-        <f>COUNTIF(F5:F32,"✓")</f>
+      <c r="D37" s="19">
+        <f>COUNTIF(F5:F35,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E34" s="20" t="inlineStr">
+      <c r="E37" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F34" s="19" t="n">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="19" t="inlineStr">
+      <c r="F37" s="19">
+        <f>COUNTIF(B5:B35,"?*")</f>
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="19" t="inlineStr">
+      <c r="B39" s="15" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="27" t="n"/>
+      <c r="E39" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F36" s="15" t="n"/>
-      <c r="G36" s="27" t="n"/>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="21" t="inlineStr">
+      <c r="F39" s="15" t="n"/>
+      <c r="G39" s="27" t="n"/>
+    </row>
+    <row r="40"/>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -1477,15 +1524,20 @@
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A37:C37"/>
+    <mergeCell ref="F39:G39"/>
     <mergeCell ref="A24:G24"/>
-    <mergeCell ref="F36:G36"/>
     <mergeCell ref="A5:G5"/>
-    <mergeCell ref="B36:D36"/>
+    <mergeCell ref="B39:D39"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G35">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F21 F22 F25 F26 F27 F28 F29 F30 F31" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F15 F16 F17 F18 F19 F20 F21 F22 F25 F26 F27 F28 F29 F30 F31 F32 F33 F34 F35" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1508,7 +1560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1563,7 +1615,7 @@
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Hecha</t>
+          <t>✓ Completada</t>
         </is>
       </c>
       <c r="G4" s="6" t="inlineStr">
@@ -1591,7 +1643,7 @@
       </c>
       <c r="B6" s="10" t="inlineStr">
         <is>
-          <t>Guardar masas en cámara de fermentación (etiquetar con fecha y hora)</t>
+          <t>Guardar masas en cámara de fermentación (etiquetar con fecha y hora) → 13 Registro de Temperaturas · Etiquetas de Elaborado</t>
         </is>
       </c>
       <c r="C6" s="11" t="inlineStr">
@@ -1618,7 +1670,7 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>Guardar pre-elaboraciones en cámara (film, etiquetar, FIFO)</t>
+          <t>Guardar pre-elaboraciones en cámara (film, etiquetar, FIFO) → 13 Registro de Temperaturas · Etiquetas de Elaborado</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1780,7 +1832,7 @@
       </c>
       <c r="B13" s="10" t="inlineStr">
         <is>
-          <t>Verificar temperaturas de cámaras (registrar en hoja de control)</t>
+          <t>Verificar temperaturas de cámaras (registrar en hoja de control) → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1848,7 +1900,7 @@
       </c>
       <c r="B17" s="10" t="inlineStr">
         <is>
-          <t>Retirar productos de vitrina (valorar si se pueden vender mañana)</t>
+          <t>Retirar el producto de vitrina y separar el sobrante: a promoción señalizada o a merma, nunca a la vitrina normal de mañana → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
@@ -1863,7 +1915,7 @@
       </c>
       <c r="E17" s="13" t="inlineStr">
         <is>
-          <t>20:00</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="F17" s="14" t="n"/>
@@ -1902,7 +1954,7 @@
       </c>
       <c r="B19" s="10" t="inlineStr">
         <is>
-          <t>Registrar mermas del día (productos descartados)</t>
+          <t>Registrar mermas del día (productos descartados) → 10 Plan de Producción Semanal · hoja Producido vs Vendido</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
@@ -1983,7 +2035,7 @@
       </c>
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>Cuadrar caja / cierre de TPV</t>
+          <t>Cuadrar caja / cierre de TPV → 09 Apertura y Cierre de Caja</t>
         </is>
       </c>
       <c r="C22" s="18" t="inlineStr">
@@ -1998,7 +2050,7 @@
       </c>
       <c r="E22" s="13" t="inlineStr">
         <is>
-          <t>20:15</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="F22" s="14" t="n"/>
@@ -2147,54 +2199,90 @@
       </c>
       <c r="E29" s="13" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="F29" s="14" t="n"/>
       <c r="G29" s="15" t="n"/>
     </row>
-    <row r="30"/>
-    <row r="31"/>
+    <row r="30">
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="13" t="n"/>
+      <c r="F30" s="14" t="n"/>
+      <c r="G30" s="15" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="28" t="n"/>
+      <c r="B31" s="10" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="12" t="n"/>
+      <c r="E31" s="13" t="n"/>
+      <c r="F31" s="14" t="n"/>
+      <c r="G31" s="15" t="n"/>
+    </row>
     <row r="32">
-      <c r="A32" s="19" t="inlineStr">
+      <c r="A32" s="28" t="n"/>
+      <c r="B32" s="10" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="12" t="n"/>
+      <c r="E32" s="13" t="n"/>
+      <c r="F32" s="14" t="n"/>
+      <c r="G32" s="15" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="28" t="n"/>
+      <c r="B33" s="10" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="12" t="n"/>
+      <c r="E33" s="13" t="n"/>
+      <c r="F33" s="14" t="n"/>
+      <c r="G33" s="15" t="n"/>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="D32" s="19">
-        <f>COUNTIF(F5:F30,"✓")</f>
+      <c r="D35" s="19">
+        <f>COUNTIF(F5:F33,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="E32" s="20" t="inlineStr">
+      <c r="E35" s="20" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="F32" s="19" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="33"/>
-    <row r="34">
-      <c r="A34" s="19" t="inlineStr">
+      <c r="F35" s="19">
+        <f>COUNTIF(B5:B33,"?*")</f>
+        <v>20.0</v>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Verificado por:</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="19" t="inlineStr">
+      <c r="B37" s="15" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="27" t="n"/>
+      <c r="E37" s="19" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
-      <c r="F34" s="15" t="n"/>
-      <c r="G34" s="27" t="n"/>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="21" t="inlineStr">
+      <c r="F37" s="15" t="n"/>
+      <c r="G37" s="27" t="n"/>
+    </row>
+    <row r="38"/>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
         <is>
           <t>— Kit de Tareas Recurrentes · Pastelería / Obrador · AI Chef Pro · aichef.pro</t>
         </is>
@@ -2202,18 +2290,23 @@
     </row>
   </sheetData>
   <mergeCells count="8">
+    <mergeCell ref="F37:G37"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="B37:D37"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F34:G34"/>
     <mergeCell ref="A25:G25"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="A35:C35"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
+  <conditionalFormatting sqref="A5:G33">
+    <cfRule type="expression" priority="2" dxfId="0">
+      <formula>$F5="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F22 F23 F26 F27 F28 F29" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"✓,—"</formula1>
+    <dataValidation sqref="F6 F7 F8 F9 F10 F11 F12 F13 F14 F17 F18 F19 F20 F21 F22 F23 F26 F27 F28 F29 F30 F31 F32 F33" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-pasteleria/01-apertura-cierre.xlsx
+++ b/astro-site/public/dl/kit-tareas-pasteleria/01-apertura-cierre.xlsx
@@ -720,7 +720,7 @@
     <row r="16">
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
+          <t>Versión 2.1 · septiembre 2026 · aichef.pro/kit-tareas-pasteleria · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
       </c>
       <c r="B25" s="10" t="inlineStr">
         <is>
-          <t>Encender las vitrinas refrigeradas y comprobar que están a 2-6 °C antes de montar → 13 Registro de Temperaturas</t>
+          <t>Encender las vitrinas refrigeradas y comprobar que están a 0-4 °C antes de montar → 13 Registro de Temperaturas</t>
         </is>
       </c>
       <c r="C25" s="18" t="inlineStr">
